--- a/public/template_lich_congtac.xlsx
+++ b/public/template_lich_congtac.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A60EA7-640F-48F3-AB5D-A24C3ADCA4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Tuan 20-2026" state="visible" r:id="rId4"/>
+    <sheet name="Tuan 20-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ĐẢNG BỘ TỈNH QUẢNG NGÃI</t>
   </si>
@@ -77,42 +78,6 @@
   </si>
   <si>
     <t>{THANH_PHAN}</t>
-  </si>
-  <si>
-    <t>Chiều</t>
-  </si>
-  <si>
-    <t>Dự Hội nghị Tỉnh ủy</t>
-  </si>
-  <si>
-    <t>Thứ Ba, ngày 12/5</t>
-  </si>
-  <si>
-    <t>Sáng</t>
-  </si>
-  <si>
-    <t>Làm việc tại cơ quan</t>
-  </si>
-  <si>
-    <t>Thứ Tư, ngày 13/5</t>
-  </si>
-  <si>
-    <t>Thứ Năm, ngày 14/5</t>
-  </si>
-  <si>
-    <t>Thứ Sáu, ngày 15/5</t>
-  </si>
-  <si>
-    <t>Thứ Bảy, ngày 16/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sáng </t>
-  </si>
-  <si>
-    <t>Nghỉ</t>
-  </si>
-  <si>
-    <t>Chủ nhật, ngày 17/5</t>
   </si>
   <si>
     <t>* Ghi chú: Ngoài thời gian đã bố trí nêu trên, các đồng chí Thường trực Đảng ủy xử lý công việc tại cơ quan hoặc đi công tác cơ sở. Khi có công việc đột xuất, phát sinh sẽ bổ sung Lịch làm việc và thông báo cho các cơ quan, đơn vị liên quan biết</t>
@@ -121,77 +86,77 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="163"/>
-      <color theme="1"/>
-      <family val="1"/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
-      <charset val="163"/>
-      <family val="1"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
       <b/>
       <u/>
-      <charset val="163"/>
-      <family val="1"/>
       <sz val="13"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
       <b/>
-      <charset val="163"/>
-      <family val="1"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
       <i/>
-      <charset val="163"/>
-      <family val="1"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
       <b/>
       <i/>
-      <charset val="163"/>
-      <family val="1"/>
       <sz val="12"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="163"/>
-      <color rgb="FFFF0000"/>
-      <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="TimesNewRomanPS-BoldMT"/>
       <charset val="163"/>
-      <color rgb="FFFF0000"/>
-      <sz val="12"/>
-      <name val="TimesNewRomanPS-BoldMT"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="163"/>
-      <color theme="1"/>
-      <family val="1"/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -274,19 +239,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -299,10 +251,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -314,12 +303,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -332,55 +315,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -716,434 +659,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="13.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="7.453125" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="13.8" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.59765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.19921875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3984375" style="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="7.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="7.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="16.8" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.6" customHeight="1">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" customHeight="1">
+      <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" customHeight="1">
+      <c r="A4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="16.2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" customHeight="1">
+      <c r="A6" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" ht="31.2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:7" ht="31.2" customHeight="1">
+      <c r="A7" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="31.2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:7" ht="31.2" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="16" t="s">
+    <row r="9" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" ht="83.4" customHeight="1">
+      <c r="A10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
-    </row>
-    <row r="20" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="20"/>
-    </row>
-    <row r="21" ht="15.6" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="20"/>
-    </row>
-    <row r="22" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-    </row>
-    <row r="23" ht="83.4" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-    </row>
-    <row r="24" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-    </row>
-    <row r="26" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-    </row>
-    <row r="27" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-    </row>
-    <row r="29" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="27"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-    </row>
-    <row r="32" ht="13.8" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+    </row>
+    <row r="11" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A17" s="14"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:7" ht="13.8" customHeight="1">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="11">
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <pageMargins left="0.7086614173228347" right="0.31496062992125984" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/public/template_lich_congtac.xlsx
+++ b/public/template_lich_congtac.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A60EA7-640F-48F3-AB5D-A24C3ADCA4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35112FC4-803F-47B4-9AE7-1D3E5582E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,6 +303,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -314,12 +320,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,32 +723,32 @@
       <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" ht="16.2" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="1:7" ht="31.2" customHeight="1">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
@@ -789,24 +789,24 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.8" customHeight="1">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:7" ht="83.4" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" ht="13.8" customHeight="1">
       <c r="A11" s="9"/>

--- a/public/template_lich_congtac.xlsx
+++ b/public/template_lich_congtac.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35112FC4-803F-47B4-9AE7-1D3E5582E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29F22B0-CACF-4D99-95C5-3BDBC5B62F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,9 +26,6 @@
     <t>ĐẢNG ỦY XÃ TRÀ BỒNG</t>
   </si>
   <si>
-    <t>{NGAY_BAN_HANH}</t>
-  </si>
-  <si>
     <t>*</t>
   </si>
   <si>
@@ -81,6 +78,9 @@
   </si>
   <si>
     <t>* Ghi chú: Ngoài thời gian đã bố trí nêu trên, các đồng chí Thường trực Đảng ủy xử lý công việc tại cơ quan hoặc đi công tác cơ sở. Khi có công việc đột xuất, phát sinh sẽ bổ sung Lịch làm việc và thông báo cho các cơ quan, đơn vị liên quan biết</t>
+  </si>
+  <si>
+    <t>Trà Bồng, {NGAY_BAN_HANH}</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,7 @@
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="18" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
@@ -702,7 +702,7 @@
     </row>
     <row r="3" spans="1:7" ht="15.6" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -713,7 +713,7 @@
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1">
       <c r="A4" s="17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -724,7 +724,7 @@
     </row>
     <row r="5" spans="1:7" ht="16.2" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -735,7 +735,7 @@
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1">
       <c r="A6" s="22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -746,46 +746,46 @@
     </row>
     <row r="7" spans="1:7" ht="31.2" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="31.2" customHeight="1">
       <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.8" customHeight="1">
@@ -799,7 +799,7 @@
     </row>
     <row r="10" spans="1:7" ht="83.4" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -903,7 +903,7 @@
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="A3:C3"/>
   </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0"/>
+  <pageMargins left="0.70866141732283472" right="0.19685039370078741" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/template_lich_congtac.xlsx
+++ b/public/template_lich_congtac.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29F22B0-CACF-4D99-95C5-3BDBC5B62F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3686BD80-CCFF-45AE-B12D-AA96B7F2AF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -291,35 +291,35 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,80 +675,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="15.6" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
       <c r="D3" s="2"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:7" ht="16.2" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" ht="31.2" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="24"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
@@ -789,24 +789,24 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.8" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" ht="83.4" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" spans="1:7" ht="13.8" customHeight="1">
       <c r="A11" s="9"/>
@@ -890,20 +890,19 @@
       <c r="G19" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:B7"/>
+  <mergeCells count="10">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.19685039370078741" top="0.78740157480314965" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.70866141732283472" right="0.19685039370078741" top="0.78740157480314965" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>